--- a/features/vehicle_setting/sandbox/vssl/vf230_vssl.xlsx
+++ b/features/vehicle_setting/sandbox/vssl/vf230_vssl.xlsx
@@ -4680,7 +4680,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Power Mode" customer setting is set to BATTERY
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K12" s="78" t="inlineStr">
@@ -4782,7 +4782,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Power Mode" customer setting is set to IGNITION
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K13" s="78" t="inlineStr">
@@ -4884,7 +4884,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K14" s="78" t="inlineStr">
@@ -4993,7 +4993,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Power Mode" customer setting is set to BATTERY
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K15" s="78" t="inlineStr">
@@ -5095,7 +5095,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Power Mode" customer setting is set to IGNITION
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K16" s="78" t="inlineStr">
@@ -5197,7 +5197,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K17" s="78" t="inlineStr">
@@ -5306,7 +5306,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K18" s="78" t="inlineStr">
@@ -5408,7 +5408,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K19" s="78" t="inlineStr">
@@ -5510,7 +5510,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K20" s="78" t="inlineStr">
@@ -5612,7 +5612,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K21" s="78" t="inlineStr">
@@ -5721,7 +5721,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K22" s="78" t="inlineStr">
@@ -5823,7 +5823,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K23" s="78" t="inlineStr">
@@ -5925,7 +5925,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K24" s="78" t="inlineStr">
@@ -6034,7 +6034,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K25" s="78" t="inlineStr">
@@ -6136,7 +6136,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 5 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K26" s="78" t="inlineStr">
@@ -6238,7 +6238,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K27" s="78" t="inlineStr">
@@ -6347,7 +6347,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K28" s="78" t="inlineStr">
@@ -6449,7 +6449,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 6 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K29" s="78" t="inlineStr">
@@ -6551,7 +6551,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K30" s="78" t="inlineStr">
@@ -7338,8 +7338,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Rear Guidance Light Status" customer setting is set to ON
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Rear Guidance Light Status" customer setting is set to ON</t>
         </is>
       </c>
       <c r="K38" s="78" t="inlineStr">
@@ -7436,8 +7435,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Rear Guidance Light Status" customer setting is set to OFF
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Rear Guidance Light Status" customer setting is set to OFF</t>
         </is>
       </c>
       <c r="K39" s="78" t="inlineStr">
@@ -7534,8 +7532,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The Vehicle Settings menu is open</t>
         </is>
       </c>
       <c r="K40" s="78" t="inlineStr">
@@ -12885,8 +12882,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Phone Repetition" customer setting is set to On
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Phone Repetition" customer setting is set to On</t>
         </is>
       </c>
       <c r="K94" s="78" t="inlineStr">
@@ -12987,8 +12983,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Phone Repetition" customer setting is set to Off
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Phone Repetition" customer setting is set to Off</t>
         </is>
       </c>
       <c r="K95" s="78" t="inlineStr">
@@ -13089,8 +13084,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The Vehicle Settings menu is open</t>
         </is>
       </c>
       <c r="K96" s="78" t="inlineStr">
@@ -18961,8 +18955,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The Vehicle Settings menu is open</t>
         </is>
       </c>
       <c r="K155" s="87" t="inlineStr">
@@ -27672,7 +27665,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K243" s="78" t="inlineStr">
@@ -27774,7 +27767,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K244" s="78" t="inlineStr">
@@ -27883,7 +27876,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K245" s="78" t="inlineStr">
@@ -27985,7 +27978,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K246" s="78" t="inlineStr">
@@ -28087,7 +28080,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K247" s="78" t="inlineStr">
@@ -28196,7 +28189,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K248" s="78" t="inlineStr">
@@ -28298,7 +28291,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K249" s="78" t="inlineStr">
@@ -28400,7 +28393,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K250" s="78" t="inlineStr">
@@ -28509,7 +28502,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Type" customer setting is set to Momentary
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K251" s="78" t="inlineStr">
@@ -28611,7 +28604,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Type" customer setting is set to Latching
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K252" s="78" t="inlineStr">
@@ -28713,7 +28706,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K253" s="78" t="inlineStr">
@@ -28822,7 +28815,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K254" s="78" t="inlineStr">
@@ -28924,7 +28917,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K255" s="78" t="inlineStr">
@@ -29026,7 +29019,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K256" s="78" t="inlineStr">
@@ -29135,7 +29128,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K257" s="78" t="inlineStr">
@@ -29237,7 +29230,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K258" s="78" t="inlineStr">
@@ -29339,7 +29332,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K259" s="78" t="inlineStr">
@@ -29448,7 +29441,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K260" s="78" t="inlineStr">
@@ -29550,7 +29543,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K261" s="78" t="inlineStr">
@@ -29652,7 +29645,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K262" s="78" t="inlineStr">
@@ -29761,7 +29754,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Hold Last State" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K263" s="78" t="inlineStr">
@@ -29863,7 +29856,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Hold Last State" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K264" s="78" t="inlineStr">
@@ -29965,7 +29958,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K265" s="78" t="inlineStr">
@@ -31781,8 +31774,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Suspension Default Ride Height" customer setting is set to Aerodynamic
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Suspension Default Ride Height" customer setting is set to Aerodynamic</t>
         </is>
       </c>
       <c r="K283" s="78" t="inlineStr">
@@ -31881,8 +31873,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Suspension Default Ride Height" customer setting is set to Normal
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Suspension Default Ride Height" customer setting is set to Normal</t>
         </is>
       </c>
       <c r="K284" s="78" t="inlineStr">
@@ -31981,8 +31972,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The Vehicle Settings menu is open</t>
         </is>
       </c>
       <c r="K285" s="78" t="inlineStr">
@@ -32187,7 +32177,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Power Mode" customer setting is set to Battery
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K287" s="78" t="inlineStr">
@@ -32289,7 +32279,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 1 Power Mode" customer setting is set to Ignition
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K288" s="78" t="inlineStr">
@@ -32391,7 +32381,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K289" s="78" t="inlineStr">
@@ -32500,7 +32490,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Power Mode" customer setting is set to Battery
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K290" s="78" t="inlineStr">
@@ -32602,7 +32592,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 2 Power Mode" customer setting is set to Ignition
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K291" s="78" t="inlineStr">
@@ -32704,7 +32694,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K292" s="78" t="inlineStr">
@@ -32813,7 +32803,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Power Mode" customer setting is set to Battery
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K293" s="78" t="inlineStr">
@@ -32915,7 +32905,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 3 Power Mode" customer setting is set to Ignition
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K294" s="87" t="inlineStr">
@@ -33017,7 +33007,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K295" s="87" t="inlineStr">
@@ -33126,7 +33116,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Power Mode" customer setting is set to Battery
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K296" s="87" t="inlineStr">
@@ -33228,7 +33218,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "SWITCH 4 Power Mode" customer setting is set to Ignition
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K297" s="87" t="inlineStr">
@@ -33330,7 +33320,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K298" s="87" t="inlineStr">
@@ -35604,8 +35594,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Ready to Drive Pop-Up" customer setting is set to On
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Ready to Drive Pop-Up" customer setting is set to On</t>
         </is>
       </c>
       <c r="K321" s="87" t="inlineStr">
@@ -35704,8 +35693,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The "Ready to Drive Pop-Up" customer setting is set to Off
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The "Ready to Drive Pop-Up" customer setting is set to Off</t>
         </is>
       </c>
       <c r="K322" s="87" t="inlineStr">
@@ -35804,8 +35792,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. The Vehicle Settings menu is open</t>
         </is>
       </c>
       <c r="K323" s="87" t="inlineStr">
@@ -36101,7 +36088,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Auto Fold Mirrors" customer setting is set to On
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Auto_Power_Folding_Mirrors = 1 (Present)</t>
         </is>
       </c>
       <c r="K326" s="87" t="inlineStr">
@@ -36199,7 +36186,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Auto Fold Mirrors" customer setting is set to Off
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Auto_Power_Folding_Mirrors = 1 (Present)</t>
         </is>
       </c>
       <c r="K327" s="87" t="inlineStr">
@@ -36297,7 +36284,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Auto_Power_Folding_Mirrors = 1 (Present)</t>
         </is>
       </c>
       <c r="K328" s="87" t="inlineStr">
@@ -46334,8 +46321,7 @@
       </c>
       <c r="J428" s="95" t="inlineStr">
         <is>
-          <t>1. The HU is in the Full-Operation state
-2. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+          <t>1. The HU is in the Full-Operation state</t>
         </is>
       </c>
       <c r="K428" s="78" t="inlineStr">
@@ -46432,8 +46418,7 @@
       </c>
       <c r="J429" s="95" t="inlineStr">
         <is>
-          <t>1. The HU is in the Full-Operation state
-2. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+          <t>1. The HU is in the Full-Operation state</t>
         </is>
       </c>
       <c r="K429" s="78" t="inlineStr">
@@ -46530,8 +46515,7 @@
       </c>
       <c r="J430" s="95" t="inlineStr">
         <is>
-          <t>1. The HU is in the Full-Operation state
-2. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+          <t>1. The HU is in the Full-Operation state</t>
         </is>
       </c>
       <c r="K430" s="78" t="inlineStr">

--- a/features/vehicle_setting/sandbox/vssl/vf230_vssl.xlsx
+++ b/features/vehicle_setting/sandbox/vssl/vf230_vssl.xlsx
@@ -4883,8 +4883,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K14" s="78" t="inlineStr">
@@ -5196,8 +5195,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K17" s="78" t="inlineStr">
@@ -5611,8 +5609,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K21" s="78" t="inlineStr">
@@ -5924,8 +5921,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K24" s="78" t="inlineStr">
@@ -6237,8 +6233,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K27" s="78" t="inlineStr">
@@ -6550,8 +6545,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 2 (Type 2)</t>
+3. PROXI AUX_Switch_Types = 2 (Type 2)</t>
         </is>
       </c>
       <c r="K30" s="78" t="inlineStr">
@@ -8321,8 +8315,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Blind_Spot_Monitoring = 1 (Present)</t>
+3. PROXI Blind_Spot_Monitoring = 1 (Present)</t>
         </is>
       </c>
       <c r="K48" s="78" t="inlineStr">
@@ -8821,8 +8814,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Passive_Entry_Menu = 1 (Present)</t>
+3. PROXI Passive_Entry_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K53" s="78" t="inlineStr">
@@ -9809,8 +9801,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Auto_Park_Brake_Menu = 1 (Present)</t>
+3. PROXI Auto_Park_Brake_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K63" s="78" t="inlineStr">
@@ -11383,8 +11374,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Auto_Door_Unlock_Menu = 1 (Present)</t>
+3. PROXI Auto_Door_Unlock_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K79" s="78" t="inlineStr">
@@ -12371,8 +12361,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K89" s="78" t="inlineStr">
@@ -12573,8 +12562,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K91" s="78" t="inlineStr">
@@ -13083,8 +13071,7 @@
       <c r="J96" s="95" t="inlineStr">
         <is>
           <t>1. The HU is in the Full-Operation state
-2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open</t>
+2. FD-CAN8 is connected to the bus simulator with signal tracing enabled</t>
         </is>
       </c>
       <c r="K96" s="78" t="inlineStr">
@@ -13487,8 +13474,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K100" s="87" t="inlineStr">
@@ -13894,8 +13880,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K104" s="78" t="inlineStr">
@@ -15484,11 +15469,10 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Heated_Seats = 0 (Absent)
-5. PROXI Else If Heated_Seats = ? (Front Seats)
-6. PROXI Remote_Start = 0 (Absent)
-7. PROXI Else If Remote_Start = ? (Present)</t>
+3. PROXI Heated_Seats = 0 (Absent)
+4. PROXI Else If Heated_Seats = ? (Front Seats)
+5. PROXI Remote_Start = 0 (Absent)
+6. PROXI Else If Remote_Start = ? (Present)</t>
         </is>
       </c>
       <c r="K120" s="78" t="inlineStr">
@@ -15893,11 +15877,10 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Heated_Seats = 0 (Absent)
-5. PROXI Else If Heated_Seats = ? (Front Seats)
-6. PROXI Remote_Start = 0 (Absent)
-7. PROXI Else If Remote_Start = ? (Present)</t>
+3. PROXI Heated_Seats = 0 (Absent)
+4. PROXI Else If Heated_Seats = ? (Front Seats)
+5. PROXI Remote_Start = 0 (Absent)
+6. PROXI Else If Remote_Start = ? (Present)</t>
         </is>
       </c>
       <c r="K124" s="78" t="inlineStr">
@@ -17169,8 +17152,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Cornering_Light = 1 (Present)</t>
+3. PROXI Cornering_Light = 1 (Present)</t>
         </is>
       </c>
       <c r="K137" s="78" t="inlineStr">
@@ -17469,8 +17451,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Greeting_Lights_Menu = 1 (Present)</t>
+3. PROXI Greeting_Lights_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K140" s="87" t="inlineStr">
@@ -18061,8 +18042,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K146" s="87" t="inlineStr">
@@ -18657,8 +18637,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Forward_Collision_Mitigation = 3 (Full Speed Forward Collision Warning with Mitigation)</t>
+3. PROXI Forward_Collision_Mitigation = 3 (Full Speed Forward Collision Warning with Mitigation)</t>
         </is>
       </c>
       <c r="K152" s="78" t="inlineStr">
@@ -19254,8 +19233,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Forward_Collision_Mitigation = 2 (Full Speed FCW with Pedestrian Emergency Braking)</t>
+3. PROXI Forward_Collision_Mitigation = 2 (Full Speed FCW with Pedestrian Emergency Braking)</t>
         </is>
       </c>
       <c r="K158" s="78" t="inlineStr">
@@ -19556,8 +19534,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Rain_Sensor = 1 (Present)</t>
+3. PROXI Rain_Sensor = 1 (Present)</t>
         </is>
       </c>
       <c r="K161" s="78" t="inlineStr">
@@ -19956,8 +19933,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Enable = ? (Enable)</t>
+3. PROXI Enable = ? (Enable)</t>
         </is>
       </c>
       <c r="K165" s="78" t="inlineStr">
@@ -20058,8 +20034,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Enable = ? (Enable)</t>
+3. PROXI Enable = ? (Enable)</t>
         </is>
       </c>
       <c r="K166" s="78" t="inlineStr">
@@ -21548,8 +21523,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Tyre_Pressure_Unit_Menu = 1 (Present)</t>
+3. PROXI Tyre_Pressure_Unit_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K181" s="78" t="inlineStr">
@@ -24296,8 +24270,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI CAN node 82 (PTGM) = 1 (Present)</t>
+3. PROXI CAN node 82 (PTGM) = 1 (Present)</t>
         </is>
       </c>
       <c r="K209" s="78" t="inlineStr">
@@ -24695,8 +24668,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI CAN node 82 (PTGM) = 1 (Present)</t>
+3. PROXI CAN node 82 (PTGM) = 1 (Present)</t>
         </is>
       </c>
       <c r="K213" s="78" t="inlineStr">
@@ -25394,8 +25366,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Traffic_Sign_Recognition_Menu = 1 (Present)</t>
+3. PROXI Traffic_Sign_Recognition_Menu = 1 (Present)</t>
         </is>
       </c>
       <c r="K220" s="78" t="inlineStr">
@@ -25994,8 +25965,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K226" s="87" t="inlineStr">
@@ -26778,8 +26748,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI FOA _Presence = 1 (Present)</t>
+3. PROXI FOA _Presence = 1 (Present)</t>
         </is>
       </c>
       <c r="K234" s="87" t="inlineStr">
@@ -27766,8 +27735,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K244" s="78" t="inlineStr">
@@ -28079,8 +28047,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K247" s="78" t="inlineStr">
@@ -28392,8 +28359,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K250" s="78" t="inlineStr">
@@ -28705,8 +28671,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K253" s="78" t="inlineStr">
@@ -29018,8 +28983,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K256" s="78" t="inlineStr">
@@ -29331,8 +29295,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K259" s="78" t="inlineStr">
@@ -29644,8 +29607,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K262" s="78" t="inlineStr">
@@ -29957,8 +29919,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K265" s="78" t="inlineStr">
@@ -31971,8 +31932,7 @@
       <c r="J285" s="95" t="inlineStr">
         <is>
           <t>1. The HU is in the Full-Operation state
-2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open</t>
+2. FD-CAN8 is connected to the bus simulator with signal tracing enabled</t>
         </is>
       </c>
       <c r="K285" s="78" t="inlineStr">
@@ -32380,8 +32340,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K289" s="78" t="inlineStr">
@@ -32693,8 +32652,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K292" s="78" t="inlineStr">
@@ -33006,8 +32964,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K295" s="87" t="inlineStr">
@@ -33319,8 +33276,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI AUX_Switch_Types = 1 (Type 1)</t>
+3. PROXI AUX_Switch_Types = 1 (Type 1)</t>
         </is>
       </c>
       <c r="K298" s="87" t="inlineStr">
@@ -33830,8 +33786,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+3. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
         </is>
       </c>
       <c r="K303" s="78" t="inlineStr">
@@ -35791,8 +35746,7 @@
       <c r="J323" s="87" t="inlineStr">
         <is>
           <t>1. The HU is in the Full-Operation state
-2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open</t>
+2. FD-CAN8 is connected to the bus simulator with signal tracing enabled</t>
         </is>
       </c>
       <c r="K323" s="87" t="inlineStr">
@@ -36870,7 +36824,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Engine Off Power Delay" customer setting is set to Fourty_Five_Sec
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Country_Code = 2 (United States of America)</t>
         </is>
       </c>
       <c r="K334" s="87" t="inlineStr">
@@ -36968,7 +36922,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Engine Off Power Delay" customer setting is set to Zero
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Country_Code = 2 (United States of America)</t>
         </is>
       </c>
       <c r="K335" s="78" t="inlineStr">
@@ -37066,7 +37020,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Engine Off Power Delay" customer setting is set to Zero
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Country_Code = 2 (United States of America)</t>
         </is>
       </c>
       <c r="K336" s="78" t="inlineStr">
@@ -37164,7 +37118,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Country_Code = 2 (United States of America)</t>
         </is>
       </c>
       <c r="K337" s="78" t="inlineStr">
@@ -37659,8 +37613,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Presence = ? (Present)</t>
+3. PROXI Presence = ? (Present)</t>
         </is>
       </c>
       <c r="K342" s="78" t="inlineStr">
@@ -38159,8 +38112,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI Twilight_Sensor = 1 (Present)</t>
+3. PROXI Twilight_Sensor = 1 (Present)</t>
         </is>
       </c>
       <c r="K347" s="78" t="inlineStr">
@@ -38463,8 +38415,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI CAN node 95 (ITBM/ITCM) = 1 (Present)</t>
+3. PROXI CAN node 95 (ITBM/ITCM) = 1 (Present)</t>
         </is>
       </c>
       <c r="K350" s="78" t="inlineStr">
@@ -39064,7 +39015,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Automatic Trailer Light Check" customer setting is set to Enable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Trailer_Light_Check = 1 (Type 1 (Radio))</t>
         </is>
       </c>
       <c r="K356" s="78" t="inlineStr">
@@ -39162,7 +39113,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The "Automatic Trailer Light Check" customer setting is set to Disable
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Trailer_Light_Check = 1 (Type 1 (Radio))</t>
         </is>
       </c>
       <c r="K357" s="78" t="inlineStr">
@@ -39260,7 +39211,7 @@
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
 3. The Vehicle Settings menu is open
-4. PENDING: DR（未取號，依審閱 §2.2：未送出前不佔號）</t>
+4. PROXI Trailer_Light_Check = 1 (Type 1 (Radio))</t>
         </is>
       </c>
       <c r="K358" s="78" t="inlineStr">
@@ -40273,8 +40224,7 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI CAN node 97 (PSSM) = 1 (Present)</t>
+3. PROXI CAN node 97 (PSSM) = 1 (Present)</t>
         </is>
       </c>
       <c r="K368" s="78" t="inlineStr">
@@ -41699,9 +41649,8 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI (Traffic_Sign_Recognition_Menu = 1 (Present)
-5. PROXI Else If (Traffic_Sign_Recognition_Menu = ? (Present)</t>
+3. PROXI (Traffic_Sign_Recognition_Menu = 1 (Present)
+4. PROXI Else If (Traffic_Sign_Recognition_Menu = ? (Present)</t>
         </is>
       </c>
       <c r="K382" s="78" t="inlineStr">
@@ -43423,9 +43372,8 @@
         <is>
           <t>1. The HU is in the Full-Operation state
 2. FD-CAN8 is connected to the bus simulator with signal tracing enabled
-3. The Vehicle Settings menu is open
-4. PROXI (Traffic_Sign_Recognition_Menu = 1 (Present)
-5. PROXI Else If (Traffic_Sign_Recognition_Menu = ? (Present)</t>
+3. PROXI (Traffic_Sign_Recognition_Menu = 1 (Present)
+4. PROXI Else If (Traffic_Sign_Recognition_Menu = ? (Present)</t>
         </is>
       </c>
       <c r="K399" s="78" t="inlineStr">
